--- a/Resources/WBS.xlsx
+++ b/Resources/WBS.xlsx
@@ -520,19 +520,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SYNCRA - WORK BREAKDOWN STRUCTURE (WBS)</t>
+          <t>BUGBOUNTYTRACK - WORK BREAKDOWN STRUCTURE (WBS)</t>
         </is>
       </c>
     </row>
@@ -543,7 +542,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -559,120 +557,156 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Student Author</t>
+          <t>Project Identifier</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Zain-Ul-Abedin (Roll No: 24-ST-038)</t>
+          <t>PTUT - PRJ - 089</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Academic Institution</t>
+          <t>Project Title</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Punjab Tianjin University of Technology (PTUT), Lahore</t>
+          <t>BugBountyTrack: Private Bug Bounty &amp; Vulnerability Disclosure Platform</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Academic Sub-Field</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Department of Software Engineering Technology</t>
+          <t>9. Cybersecurity, Privacy &amp; LegalTech</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Project Supervisor</t>
+          <t>Single Accountable Author</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Sir Umar Hayat</t>
+          <t>Taha Asadullah (Roll No: 24-ST-013)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Standard Compliance</t>
+          <t>Academic Institution</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>IEEE Std 830-1998 / ISO/IEC/IEEE 29148:2018</t>
+          <t>Punjab Tianjin University of Technology (PTUT), Lahore</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Client Platform</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Flutter 3.24+ (Dart 3.5+, Clean Architecture, Riverpod, Drift SQLite)</t>
+          <t>Department of Software Engineering Technology</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Backend &amp; Admin Engine</t>
+          <t>Session / Batch / Section</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Unified Next.js 14+ Fullstack (Admin CRM + REST API Gateway) on Vercel</t>
+          <t>Session 2024–2028 / Batch 24-SET-Fall / Section SET-A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Persistence Tier</t>
+          <t>Official Student Email</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>MongoDB Atlas Shared Cluster (Mongoose ORM)</t>
+          <t>24-st-013@students.ptut.edu.pk</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Target Test Device</t>
+          <t>Project Supervisor</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Sparx Note 20 (Physical Android 13 Hardware via USB Debugging)</t>
+          <t>Sir Umar Hayat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>Client Platform</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Modern Web (Next.js 14+ App Router, React 18+, TypeScript 5.x, Tailwind CSS, OpenPGP.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Backend &amp; Persistence</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Unified Next.js Serverless on Vercel + PostgreSQL 16 on Neon via Prisma ORM (RLS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Planned Workload</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>352 Total Hours (264h Academic Baseline + 88h Commercial Extension)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>Release State</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Version 2.0.0 (Flutter Multi-Platform &amp; Modular Academic Baseline)</t>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Commercial Baseline &amp; Academic Evaluation Specification (Version 3.1.0)</t>
         </is>
       </c>
     </row>
@@ -687,17 +721,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
-    <col width="92" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,35 +744,45 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
+          <t>Req ID</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
           <t>Module / Area</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Work Package Name</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Deliverable Scope &amp; Acceptance Criteria</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>Lead Squad Role</t>
-        </is>
-      </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
+          <t>Start–End Week</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
           <t>Est. Hours</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Human Owner</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Predecessor</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -748,35 +794,45 @@
           <t>WP-1.1</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>MOD-1: Architecture &amp; Foundation</t>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>FR-1.1</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Monorepo &amp; CI/CD Pipeline Inception</t>
+          <t>MOD-1: Foundation &amp; Security</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>GitHub Actions workflows for Android release APK and Vercel Next.js readiness</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>DevOps (Aizen)</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Monorepo Scaffolding &amp; CI Pipeline</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Next.js 14+ monorepo, ESLint, Prettier, and GitHub Actions CI workflow</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>[DONE]</t>
         </is>
@@ -788,35 +844,45 @@
           <t>WP-1.2</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>MOD-1: Architecture &amp; Foundation</t>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>FR-8.2</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Matcha Noir Visual Token Specification</t>
+          <t>MOD-1: Foundation &amp; Security</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Design token definitions in Flutter (Obsidian, Charcoal, Matcha Lime, Soft Mint)</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>UI/UX (Robin)</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="n">
+          <t>PostgreSQL Schema &amp; Row-Level Security</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Prisma relational schema, PostgreSQL RLS tenant context, and append-only audit grants</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>WP-1.1</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>[DONE]</t>
         </is>
@@ -828,37 +894,47 @@
           <t>WP-1.3</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>MOD-1: Architecture &amp; Foundation</t>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>FR-8.1</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Drift SQLite Local Storage &amp; DAO</t>
+          <t>MOD-1: Foundation &amp; Security</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Type-safe SQLite database schema with indexed FIFO mutation queue table</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Architect (Kisuke)</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+          <t>Early Markdown AST Sanitization Engine</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>`rehype-sanitize` pipeline neutralizing OWASP XSS cheat sheet attack vectors</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>WP-1.1</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>[IN PROGRESS]</t>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>[DONE]</t>
         </is>
       </c>
     </row>
@@ -868,37 +944,47 @@
           <t>WP-1.4</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>MOD-1: Architecture &amp; Foundation</t>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Hardware-Backed Token Encryption</t>
+          <t>MOD-1: Foundation &amp; Security</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>flutter_secure_storage integration with iOS Keychain &amp; Android KeyStore</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Security (Riza)</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>WP-1.3</t>
-        </is>
+          <t>Design Tokens &amp; Accessible UI Base</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Tailwind CSS tokens meeting WCAG 2.2 AA (24 × 24 px touch targets)</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>[READY]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>WP-1.1</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>[DONE]</t>
         </is>
       </c>
     </row>
@@ -908,37 +994,47 @@
           <t>WP-2.1</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>MOD-2: Onboarding &amp; Auth</t>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>FR-1.3</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Welcome Greetings &amp; Abstract Visual Art</t>
+          <t>MOD-2: Identity &amp; Multi-Tenancy</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Greeting screen with geometric semicircle Matcha visual art and CTA routing</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>UI/UX (Robin)</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>WP-1.2</t>
-        </is>
+          <t>Tenant Registration Wizard &amp; Profiles</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Organization creation, slug reservation, and public program profile</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>W3–W4</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>[ACTIVE]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>WP-1.4</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>[READY]</t>
         </is>
       </c>
     </row>
@@ -948,37 +1044,47 @@
           <t>WP-2.2</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>MOD-2: Onboarding &amp; Auth</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>FR-1.3</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>3-Step Interactive Onboarding Carousel</t>
+          <t>MOD-2: Identity &amp; Multi-Tenancy</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Swipeable PageView slides, animated dot indicators, back/forward navigation and skip</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>UI/UX (Robin)</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+          <t>Email / Password Auth &amp; JWT Sessions</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Bcrypt password hashing (rounds = 12) and signed HTTP-only JWT cookies</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>W3–W4</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>WP-2.1</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>[ACTIVE]</t>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -988,37 +1094,47 @@
           <t>WP-2.3</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>MOD-2: Onboarding &amp; Auth</t>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>FR-1.2</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Authentic Student Registration &amp; Validation</t>
+          <t>MOD-2: Identity &amp; Multi-Tenancy</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Live form validation for student name, roll number, university, major, password</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Frontend (Robin)</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
+          <t>Server-Enforced RBAC Middleware</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Access control enforcing Owner, Defender, Hunter, and ReadOnly roles</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>W3–W4</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>WP-2.2</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>[ACTIVE]</t>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1028,37 +1144,47 @@
           <t>WP-2.4</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>MOD-2: Onboarding &amp; Auth</t>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>FR-8.3</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Sub-Second OTP &amp; Guest Mode Engine</t>
+          <t>MOD-2: Identity &amp; Multi-Tenancy</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>6-digit OTP delivery via Resend API and instant 'Continue as Guest' fresh start</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Backend (Diablo)</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>WP-2.3</t>
-        </is>
+          <t>Token-Bucket Rate Limiter &amp; Pool RLS</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Token-bucket rate limiting (5 req/hr/IP) on intake + dynamic tenant RLS</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>W3–W4</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>[ACTIVE]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>WP-1.2</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1068,37 +1194,47 @@
           <t>WP-3.1</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>MOD-3: Daily Habits &amp; Velocity</t>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>FR-2.1</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Multi-Cadence Habit Creator</t>
+          <t>MOD-3: Policy &amp; Cryptography Base</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Habit creation across Daily, Weekly, Monthly, and Quarterly schedules</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>WP-2.4</t>
-        </is>
+          <t>RFC 9116 security.txt Endpoint &amp; Download</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Compliant RFC 9116 text policy preview and download route per tenant</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>W5–W6</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>WP-2.1</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1108,37 +1244,47 @@
           <t>WP-3.2</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>MOD-3: Daily Habits &amp; Velocity</t>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>FR-2.2</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Single-Tap Habit Toggle with Haptics</t>
+          <t>MOD-3: Policy &amp; Cryptography Base</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Instant local Drift write with low-latency tactile haptic feedback (&lt;15ms)</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Frontend (Robin)</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
+          <t>In-Browser Cleartext PGP Signing UI</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Browser workflow signing security.txt inline using private signing key</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>W5–W6</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>WP-3.1</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>[BACKLOG]</t>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1148,37 +1294,47 @@
           <t>WP-3.3</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>MOD-3: Daily Habits &amp; Velocity</t>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>FR-2.5</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Daily Goal Ring Velocity Metric</t>
+          <t>MOD-3: Policy &amp; Cryptography Base</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Dynamic circular completion percentage calculation (0% to 100%)</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>WP-3.2</t>
-        </is>
+          <t>DNS TXT Challenge Ownership Verifier</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Node.js DNS challenge record lookup verifying domain ownership</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>W5–W6</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>WP-3.1</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1188,37 +1344,47 @@
           <t>WP-3.4</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>MOD-3: Daily Habits &amp; Velocity</t>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>FR-3.1</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>7-Day Interactive Calendar Strip</t>
+          <t>MOD-3: Policy &amp; Cryptography Base</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Day-by-day capsule strip with leap-year invariant date calculations</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Frontend (Robin)</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>WP-3.3</t>
-        </is>
+          <t>WebCrypto Keypair Generator &amp; KeyStore</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Ed25519 signing + X25519/RSA encryption subkeys in encrypted IndexedDB</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>W5–W6</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>WP-2.2</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1228,37 +1394,47 @@
           <t>WP-4.1</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>MOD-4: Streak Calculus &amp; Shields</t>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>FR-3.3</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Contiguous Day Streak Arithmetic</t>
+          <t>MOD-4: Cryptographic Intake &amp; CVSS</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Closed-form contiguous day verification anchored to user local ISO-8601 calendar</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
+          <t>Dual-Recipient OpenPGP Payload Encrypt</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>In-browser payload encryption targeting Org encryption subkey + Hunter key with neutral operational labels</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>W7–W8</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>WP-3.4</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>[BACKLOG]</t>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1268,37 +1444,47 @@
           <t>WP-4.2</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>MOD-4: Streak Calculus &amp; Shields</t>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>FR-3.4</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>48-Hour Recovery Shield Auto-Consume</t>
+          <t>MOD-4: Cryptographic Intake &amp; CVSS</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Automatic consumption of 1 shield upon missed day to grant 48h recovery grace window</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
+          <t>Encrypted Attachment Upload (Cloudflare R2)</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Client-side encrypted streaming binary uploads (≤ 25 MB) to R2</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>W7–W8</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>WP-4.1</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>[BACKLOG]</t>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1308,37 +1494,47 @@
           <t>WP-4.3</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>MOD-4: Streak Calculus &amp; Shields</t>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>FR-4.1</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Double-Miss Reset Invariant</t>
+          <t>MOD-4: Cryptographic Intake &amp; CVSS</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Streak reset to 0 upon shield exhaustion while preserving all-time Best Streak</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>WP-4.2</t>
-        </is>
+          <t>Pure TypeScript CVSS 3.1 &amp; 52-Vector Test</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>8 Base metric scoring engine asserting 100% parity across FIRST.org suite in CVSS_TEST_FIXTURES.md</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>W7–W8</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>WP-1.1</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1348,37 +1544,47 @@
           <t>WP-4.4</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>MOD-4: Streak Calculus &amp; Shields</t>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>FR-5.1</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>7-Day Shield Regeneration Loop</t>
+          <t>MOD-4: Cryptographic Intake &amp; CVSS</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Earn +1 Streak Recovery Shield every 7 contiguous days (max capacity 2)</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>WP-4.3</t>
-        </is>
+          <t>In-Browser Decrypt &amp; Basic Triage State</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Passphrase key unlocking, decrypted triage view, and basic state transitions (NEW-&gt;TRIAGING-&gt;ACCEPTED); Week 7 Live Working Prototype</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>W7–W8</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>WP-4.1</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1594,47 @@
           <t>WP-5.1</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>MOD-5: Coursework &amp; Gantt Hub</t>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>FR-5.2</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Course Enrollment &amp; Code Ledger</t>
+          <t>MOD-5: Triage &amp; Commit Verification</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Course code, title, credit hours, instructor name, and syllabus registry</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>WP-2.4</t>
-        </is>
+          <t>Dual-Lane Threading Interface</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Confidential conversation thread and private reviewer-only internal notes</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>W9–W10</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>WP-4.4</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1428,37 +1644,47 @@
           <t>WP-5.2</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>MOD-5: Coursework &amp; Gantt Hub</t>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>FR-5.3</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Exam Countdown Urgency Clocks</t>
+          <t>MOD-5: Triage &amp; Commit Verification</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Real-time countdown widgets displaying remaining days with color urgency tags</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Frontend (Robin)</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
+          <t>Metadata Notifications &amp; Duplicate Link</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Resend email dispatching metadata only; reviewer-driven duplicate linking</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>W9–W10</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>WP-5.1</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>[BACKLOG]</t>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1468,37 +1694,47 @@
           <t>WP-5.3</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>MOD-5: Coursework &amp; Gantt Hub</t>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>FR-6.2</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Multi-Milestone Coursework Decomposition</t>
+          <t>MOD-5: Triage &amp; Commit Verification</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Sub-milestone breakdown (Research, Draft, Code, Verification, Final Submission)</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>WP-5.2</t>
-        </is>
+          <t>GitHub REST API Commit SHA &amp; Author Check</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>GitHub API v3 lookup validating commit existence, author, and branch for public and private repos</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>W9–W10</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>WP-5.1</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1508,37 +1744,47 @@
           <t>WP-5.4</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>MOD-5: Coursework &amp; Gantt Hub</t>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>FR-6.3</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Interactive Gantt Progress Bars</t>
+          <t>MOD-5: Triage &amp; Commit Verification</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Dynamic horizontal Gantt milestone visualization (0% to 100%)</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Frontend (Robin)</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
+          <t>Infrastructure Config SHA-256 Hash Binder</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Non-code remediation hash generator and deployment environment recording</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>W9–W10</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>WP-5.3</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>[BACKLOG]</t>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1548,37 +1794,47 @@
           <t>WP-6.1</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>MOD-6: Timetable &amp; Attendance Radar</t>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>FR-7.2</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Weekly Academic Timetable Visualizer</t>
+          <t>MOD-6: Attested Retest &amp; Defense</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Interactive timetable grid with lecture time blocks, room/lab numbers, and instructors</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Frontend (Robin)</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>WP-5.4</t>
-        </is>
+          <t>Attested Retest State Machine &amp; Closure</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Attested retest state machine (3 distinct fan-out terminal states), failed retest loopback to ACCEPTED, and ticket reopening</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>W11–W12</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>WP-5.3</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -1588,609 +1844,659 @@
           <t>WP-6.2</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>MOD-6: Timetable &amp; Attendance Radar</t>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>FR-8.4</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>75% Attendance Deficit Defense Calculator</t>
+          <t>MOD-6: Attested Retest &amp; Defense</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Real-time attendance % calculation with proactive deficit alerts before 75% threshold</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>WP-6.1</t>
-        </is>
+          <t>Storage Quota Monitor &amp; Enforcer</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Quota enforcement (50 MB DB per tenant / 512 MB Neon, 2 GB R2 per tenant / 10 GB free tier; 90% warning, 100% rejection)</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>W11–W12</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>6</v>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>WP-1.2</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>WP-6.3</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>MOD-6: Timetable &amp; Attendance Radar</t>
+          <t>ACAD-01</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>EV-01</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Room &amp; Lecture Schedule Clash Radar</t>
+          <t>ACAD: Evaluation &amp; Usability</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Overlapping lecture and exam slot conflict detection engine</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>WP-6.2</t>
-        </is>
+          <t>Controlled Peer Usability Study</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Controlled evaluation with 3–5 peers across OWASP Juice Shop targets</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>W11–W12</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>WP-6.1</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>WP-6.4</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>MOD-6: Timetable &amp; Attendance Radar</t>
+          <t>ACAD-02</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>EV-02</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Attendance Gamification &amp; XP Rewards</t>
+          <t>ACAD: Evaluation &amp; Usability</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Award +15 XP weekly and 'Academic Rigor' badge for maintaining &gt;= 80% attendance</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>WP-6.3</t>
-        </is>
+          <t>Final Project Report &amp; Live Demo Defense</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Comprehensive academic report, presentation slides, and defense demo</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>W11–W12</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>14</v>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>ACAD-01</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>WP-7.1</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>MOD-7: Team Rooms &amp; Quorum</t>
+          <t>WP-BUF</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Capstone &amp; Study Team Room Creation</t>
+          <t>GOV: Contingency &amp; Buffer</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Team room creation, invite code generation, and member enrollment</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Backend (Kisuke)</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>WP-2.4</t>
-        </is>
+          <t>Project Buffer &amp; Defense Contingency</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Distributed buffer for unexpected debugging, security fixes &amp; defense trials</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>W1–W12</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>28</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>WP-1.1</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>WP-7.2</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>MOD-7: Team Rooms &amp; Quorum</t>
+          <t>WP-7.1</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>FR-1.3</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Shared M-of-N Quorum Sprint Contracts</t>
+          <t>MOD-7: Commercial Launch</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Configurable quorum check-in requirement to advance collective team streaks</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>WP-7.1</t>
-        </is>
+          <t>Auth Hardening &amp; Session Revocation</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>TOTP MFA enrollment, password reset with immediate session revocation (JWT jti blacklisting), and MFA recovery codes</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>W13–W14</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>WP-2.2</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>WP-7.3</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>MOD-7: Team Rooms &amp; Quorum</t>
+          <t>WP-7.2</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>FR-1.4</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Live Activity Feed &amp; Member Check-in</t>
+          <t>MOD-7: Commercial Launch</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Real-time team check-in stream across Next.js API Gateway</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Backend (Kisuke)</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>WP-7.2</t>
-        </is>
+          <t>Guided Onboarding &amp; Domain Verification</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Step-by-step wizard: DNS TXT verification, PGP key generation, RFC 9116 download, and public program activation</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>W13–W14</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>WP-3.2</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>WP-7.4</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>MOD-7: Team Rooms &amp; Quorum</t>
+          <t>WP-7.3</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>FR-1.5</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Peer Accountability Nudge Dispatch</t>
+          <t>MOD-7: Commercial Launch</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Automated peer reminder nudges sent to teammates 4h prior to daily cutoff</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Frontend (Robin)</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="n">
+          <t>Private Program Access &amp; Invite Lifecycle</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Cryptographic invitation tokens (`token_hash` SHA-256 storage, 72h expiry, one-time redemption, uninvited email rejection)</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>W13–W14</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>WP-7.3</t>
-        </is>
-      </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>WP-2.1</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>WP-8.1</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>MOD-8: Syncra Plus &amp; Sparks Economy</t>
+          <t>WP-7.4</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>FR-3.6</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Entitlement Guard &amp; Subscription Gating</t>
+          <t>MOD-7: Commercial Launch</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Free Scholar Base vs Syncra Plus subscription entitlement checks</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Security (Riza)</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>WP-2.4</t>
-        </is>
+          <t>Multi-Defender Keying &amp; Session Re-Wrapping</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Local key export UI, program keyring versioning (`recipient_set_version`), and audited historical session-key re-wrapping</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>W15–W16</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>WP-3.4</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>WP-8.2</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>MOD-8: Syncra Plus &amp; Sparks Economy</t>
+          <t>WP-7.5</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>FR-5.4</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>'Syncra Sparks' Virtual Currency Ledger</t>
+          <t>MOD-7: Commercial Launch</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Double-entry token ledger tracking earned and purchased sparks balances</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Domain (Diablo)</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>WP-8.1</t>
-        </is>
+          <t>Notification Outbox Worker &amp; Deduplication</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Outbox table pattern, exponential backoff retries, idempotency keys (no duplicate alerts), and minimal-metadata email templates</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>W15–W16</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>WP-5.2</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>WP-8.3</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>MOD-8: Syncra Plus &amp; Sparks Economy</t>
+          <t>WP-7.6</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>FR-7.5</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>In-App Cosmetic &amp; Perk Store</t>
+          <t>MOD-7: Commercial Launch</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Marketplace for redeeming sparks for Matcha themes, ringtones, badge frames, and shields</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Frontend (Robin)</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>WP-8.2</t>
-        </is>
+          <t>Redacted Evidence Export Engine</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Browser-side PDF/JSON export after local decryption. Excludes free-text exploit details by default; includes full preview before download</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>W15–W16</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>WP-6.1</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>WP-8.4</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>MOD-8: Syncra Plus &amp; Sparks Economy</t>
+          <t>WP-7.7</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>FR-8.4</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Payment Gateway &amp; Webhook Verification</t>
+          <t>MOD-7: Commercial Launch</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Stripe REST API Sandbox and In-App Purchase cryptographic webhook verification</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Backend (Kisuke)</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>WP-8.3</t>
-        </is>
+          <t>Production Cloud &amp; Stripe Subscriptions</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Stripe Checkout, Customer Portal, webhook idempotency, failed payment grace periods, cancellation downgrade, and seat entitlement checks</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>W17–W18</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>14</v>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>WP-1.1</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>WP-9.1</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>MOD-9: SuperAdmin Control Center</t>
+          <t>WP-7.8</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>FR-8.5</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Live Student CRM Ledger &amp; Roster</t>
+          <t>MOD-7: Commercial Launch</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Searchable student directory with verified roll number, major, batch, and streak health</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Admin (Mayuri)</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>WP-2.4</t>
-        </is>
+          <t>Disaster Recovery &amp; Incident Runbooks</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Automated daily PostgreSQL + R2 backup restore drill in sandbox, customer hard-deletion workflow, and incident response runbook</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>W17–W18</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>WP-1.2</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>WP-9.2</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>MOD-9: SuperAdmin Control Center</t>
+          <t>WP-7.9</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>GOV-02</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Live OTP Monitor &amp; One-Click Bypass</t>
+          <t>GOV: Contingency &amp; Buffer</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Real-time OTP terminal with 5m countdown clocks and instant supervisor verification</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Admin (Mayuri)</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>WP-9.1</t>
-        </is>
+          <t>Commercial Launch Contingency Buffer</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Buffer for unexpected billing edge cases, webhook debugging, and production pilot support</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>W13–W18</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>[BACKLOG]</t>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>WP-7.1</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>WP-9.3</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>MOD-9: SuperAdmin Control Center</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>Emergency Shield &amp; XP Override Ledger</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Manual administrative +1 Streak Recovery Shield grant modal and XP auditing</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Admin (Mayuri)</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>WP-9.2</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>[BACKLOG]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>WP-9.4</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>MOD-9: SuperAdmin Control Center</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Sync Telemetry &amp; Queue Health Monitor</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Mutation queue throughput, error log auditing, and MongoDB connection metrics</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>DevOps (Aizen)</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>WP-9.3</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>[BACKLOG]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="D38" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED ENGINEERING HOURS:</t>
         </is>
       </c>
-      <c r="F38" s="14">
-        <f>SUM(F2:F37)</f>
-        <v/>
+      <c r="G36" s="14">
+        <f>SUM(G2:G35)</f>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -2204,20 +2510,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2233,47 +2534,22 @@
       </c>
       <c r="C1" s="15" t="inlineStr">
         <is>
-          <t>Siesta (PM)</t>
+          <t>Human Accountable (Taha)</t>
         </is>
       </c>
       <c r="D1" s="15" t="inlineStr">
         <is>
-          <t>Kisuke (Arch)</t>
+          <t>Supervisor (Sir Umar)</t>
         </is>
       </c>
       <c r="E1" s="15" t="inlineStr">
         <is>
-          <t>Diablo (Domain)</t>
+          <t>Faculty Panel (PTUT)</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
         <is>
-          <t>Robin (UX)</t>
-        </is>
-      </c>
-      <c r="G1" s="15" t="inlineStr">
-        <is>
-          <t>Aizen (DevOps)</t>
-        </is>
-      </c>
-      <c r="H1" s="15" t="inlineStr">
-        <is>
-          <t>Yoruichi (QA)</t>
-        </is>
-      </c>
-      <c r="I1" s="15" t="inlineStr">
-        <is>
-          <t>Riza (Sec)</t>
-        </is>
-      </c>
-      <c r="J1" s="15" t="inlineStr">
-        <is>
-          <t>Mayuri (R&amp;D)</t>
-        </is>
-      </c>
-      <c r="K1" s="15" t="inlineStr">
-        <is>
-          <t>Yamamoto (Audit)</t>
+          <t>Internal AI Advisory Squad</t>
         </is>
       </c>
     </row>
@@ -2285,52 +2561,27 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Architecture &amp; Zero-Cost Foundation</t>
+          <t>Foundation, RLS &amp; Markdown Sanitization</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A / R</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Advised by Arthur (Arch) &amp; Cyra (Sec)</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2593,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Onboarding &amp; Student Authentication</t>
+          <t>Multi-Tenancy, Auth &amp; Server RBAC</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A / R</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -2357,37 +2608,12 @@
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Advised by Marcus (Forge) &amp; Cyra (Sec)</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2625,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Daily Habits &amp; Multi-Cadence Velocity</t>
+          <t>RFC 9116 Policy &amp; Browser Keygen</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A / R</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -2414,37 +2640,12 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Advised by Victoria (Req) &amp; Cyra (Sec)</t>
         </is>
       </c>
     </row>
@@ -2456,52 +2657,27 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Streak Calculus &amp; 48h Recovery Shields</t>
+          <t>Client Cryptography &amp; CVSS 3.1</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A / R</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Advised by Cyra (Sec) &amp; Elena (QA)</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2689,12 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Coursework &amp; Milestone Gantt Hub</t>
+          <t>Confidential Triage &amp; GitHub Validation</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A / R</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -2528,37 +2704,12 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Advised by Marcus (Forge) &amp; Julian (UX)</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2721,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Smart Timetable &amp; 75% Attendance Radar</t>
+          <t>Attested Retest, Peer Study &amp; Defense</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A / R</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -2585,208 +2736,12 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>MOD-7</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Student Team Rooms &amp; Quorum Contracts</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>MOD-8</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Syncra Plus &amp; 'Syncra Sparks' Economy</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>MOD-9</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>SuperAdmin Control Center &amp; CRM</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Advised by Elena (QA) &amp; Alexander (PM)</t>
         </is>
       </c>
     </row>
@@ -2801,15 +2756,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="83" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2820,7 +2776,7 @@
       </c>
       <c r="B1" s="15" t="inlineStr">
         <is>
-          <t>Sprint Name</t>
+          <t>Academic Weeks</t>
         </is>
       </c>
       <c r="C1" s="15" t="inlineStr">
@@ -2830,15 +2786,20 @@
       </c>
       <c r="D1" s="15" t="inlineStr">
         <is>
-          <t>Key Engineering Deliverable</t>
+          <t>Key Engineering Deliverables</t>
         </is>
       </c>
       <c r="E1" s="15" t="inlineStr">
         <is>
-          <t>Hardware Target</t>
+          <t>Prerequisite Gates &amp; Evaluation</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>Planned Hours</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2850,27 +2811,30 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Project Inception &amp; SRS Transformation</t>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Weeks 1–2</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>WP-1.1, WP-1.2</t>
+          <t>WP-1.1, WP-1.2, WP-1.3, WP-1.4, Buffer (4h)</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Monorepo scaffolding, Flutter 3.24+, Next.js Admin, CI/CD, Docs/SRS.docx</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>CI/CD &amp; Local Host</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
+          <t>Monorepo scaffolding, PostgreSQL RLS schema, AST Markdown sanitization, design tokens, BRD, SRS, WBS</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Phase Gate 1 (DoR) Certified</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>[DONE]</t>
         </is>
@@ -2882,29 +2846,32 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Interactive Onboarding &amp; Student Auth Flow</t>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Weeks 3–4</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>WP-2.1, WP-2.2, WP-2.3, WP-2.4</t>
+          <t>WP-2.1, WP-2.2, WP-2.3, WP-2.4, Buffer (4h)</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Welcome Greeting, 3-slide Onboarding carousel, Login/Register forms, Guest Mode</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Sparx Note 20 (USB)</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>[ACTIVE]</t>
+          <t>Tenant registration wizard, bcrypt auth, JWT cookies, server RBAC, token-bucket rate limiter</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Phase Gate 2 (DoAC) Architecture</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>[READY]</t>
         </is>
       </c>
     </row>
@@ -2914,27 +2881,30 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Habit Velocity Engine &amp; Streak Calculus</t>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Weeks 5–6</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>WP-3.1..WP-3.4, WP-4.1..WP-4.4</t>
+          <t>WP-3.1, WP-3.2, WP-3.3, WP-3.4, Buffer (4h)</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Habit CRUD, 7-day capsule strip, 48h Recovery Shield state machine</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Sparx Note 20 (USB)</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
+          <t>Dynamic security.txt download API, browser cleartext PGP signing, DNS TXT check, WebCrypto keypairs</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Phase Gate 3 (DoCC) Core Crypto</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>[PLANNED]</t>
         </is>
@@ -2946,27 +2916,30 @@
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Coursework Gantt &amp; 75% Attendance Radar</t>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Weeks 7–8</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>WP-5.1..WP-5.4, WP-6.1..WP-6.4</t>
+          <t>WP-4.1, WP-4.2, WP-4.3, WP-4.4, Buffer (4h)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Milestone Gantt bars, weekly timetable grid, 75% deficit danger radar</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Sparx Note 20 (USB)</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
+          <t>Multi-recipient payload encryption, R2 attachment upload, CVSS 3.1 engine, in-browser decryption, basic triage</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Week 7 Live Working Prototype Milestone</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>[PLANNED]</t>
         </is>
@@ -2978,27 +2951,30 @@
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Team Rooms &amp; Syncra Plus Sparks Economy</t>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Weeks 9–10</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>WP-7.1..WP-7.4, WP-8.1..WP-8.4</t>
+          <t>WP-5.1, WP-5.2, WP-5.3, WP-5.4, Buffer (6h)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Quorum sprint contracts, Sparks token ledger, cosmetic theme store</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Sparx Note 20 (USB)</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
+          <t>Dual-lane triage threads, Resend metadata alerts, duplicate linking, GitHub REST API commit validation</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Phase Gate 4 (DoQV) Triage &amp; VCS</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>[PLANNED]</t>
         </is>
@@ -3010,30 +2986,114 @@
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>SuperAdmin CRM &amp; Final FYP Submission</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Weeks 11–12</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>WP-9.1..WP-9.4</t>
+          <t>WP-6.1, WP-6.2, ACAD-01, ACAD-02, Buffer (6h)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Live OTP monitor terminal, student verification CRM, final APK release build</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Sparx Note 20 (USB)</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
+          <t>Attested retest engine, storage quotas, peer study (3–5 peers), Final FYP Report &amp; Defense</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Final FYP Defense &amp; Demonstration</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>[PLANNED]</t>
         </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Weeks 13–15</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>WP-7.1, WP-7.2, WP-7.3, WP-7.4, Buffer (4h)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>TOTP MFA, session revocation, guided onboarding wizard, tokenized private programs, multi-defender key management</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Milestone 3: Controlled Commercial Pilot</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Weeks 16–18</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>WP-7.5, WP-7.6, WP-7.7, WP-7.8, Buffer (6h)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Notification outbox worker, redacted evidence export engine, Stripe subscription lifecycle, DR sandbox restore</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Milestone 4: Commercial Launch Gate (DoRG)</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL PLANNED SPRINT HOURS:</t>
+        </is>
+      </c>
+      <c r="F10" s="14">
+        <f>SUM(F2:F9)</f>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -3047,14 +3107,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3065,17 +3125,17 @@
       </c>
       <c r="B1" s="15" t="inlineStr">
         <is>
-          <t>Vendor / Provider</t>
+          <t>Platform Provider</t>
         </is>
       </c>
       <c r="C1" s="15" t="inlineStr">
         <is>
-          <t>Quota / Resource Tier</t>
+          <t>Provisioned Cloud Tier</t>
         </is>
       </c>
       <c r="D1" s="15" t="inlineStr">
         <is>
-          <t>Target Usage</t>
+          <t>Resource Allocations &amp; Quotas</t>
         </is>
       </c>
       <c r="E1" s="15" t="inlineStr">
@@ -3087,22 +3147,22 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Mobile Client Runtime</t>
+          <t>Client Web &amp; API Gateway</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Flutter SDK / Google</t>
+          <t>Vercel Cloud</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Open Source BSD-3</t>
+          <t>Hobby / Free Tier</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Cross-platform mobile compilation</t>
+          <t>Serverless Functions, Edge CDN, Global SSL</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
@@ -3112,22 +3172,22 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Web Hosting &amp; API Gateway</t>
+          <t>Relational Database</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Vercel Free Tier</t>
+          <t>Neon Serverless Cloud</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>100 GB Bandwidth, Serverless Functions</t>
+          <t>Free Tier</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Next.js Admin CRM &amp; REST Gateway</t>
+          <t>PostgreSQL 16 (512 MB Storage, Shared Compute, Dynamic RLS)</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
@@ -3137,22 +3197,22 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Persistence &amp; Database</t>
+          <t>Encrypted Object Storage</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>MongoDB Atlas Shared</t>
+          <t>Cloudflare R2</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>512 MB Storage, M0 Sandbox Cluster</t>
+          <t>Free Tier</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Student profiles, habits, and ledger</t>
+          <t>10 GB Storage, Zero Egress Fees</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
@@ -3162,22 +3222,22 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Transactional Email Delivery</t>
+          <t>Transactional Email</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Resend API Free Tier</t>
+          <t>Resend API</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>3,000 Emails / Month, Sub-second OTP</t>
+          <t>Free Developer Tier</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Student verification OTP codes</t>
+          <t>100 Emails / Day, 3,000 Emails / Month</t>
         </is>
       </c>
       <c r="E5" s="17" t="n">
@@ -3187,22 +3247,22 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Payment &amp; Virtual Economy</t>
+          <t>Source Code &amp; CI/CD</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Stripe API Sandbox</t>
+          <t>GitHub Free Tier</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Test Mode Developer Environment</t>
+          <t>Public Repository</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Syncra Plus &amp; Sparks transactions</t>
+          <t>2,000 Action Minutes / Month, REST API v3 Integration</t>
         </is>
       </c>
       <c r="E6" s="16" t="n">
@@ -3212,22 +3272,22 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>CI/CD Build Automation</t>
+          <t>DNS Resolution</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>GitHub Actions</t>
+          <t>System DNS Resolver</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2,000 Free Build Minutes / Month</t>
+          <t>Free Native</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Android release APK compilation</t>
+          <t>Node.js `dns.promises` Resolver for Domain Validation</t>
         </is>
       </c>
       <c r="E7" s="17" t="n">
@@ -3237,22 +3297,22 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Version Control &amp; Remote</t>
+          <t>Domain &amp; SSL</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>GitHub Private Repository</t>
+          <t>Local / Vercel Subdomain</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Unlimited Private Repositories</t>
+          <t>Free Tier</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Monorepo source code &amp; assets</t>
+          <t>`.vercel.app` Free Subdomain with Automatic TLS Certificate</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
@@ -3260,14 +3320,189 @@
       </c>
     </row>
     <row r="9">
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL MONTHLY INFRASTRUCTURE COST:</t>
-        </is>
-      </c>
-      <c r="E9" s="18">
-        <f>SUM(E2:E8)</f>
-        <v/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Production Web Hosting</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Vercel Pro</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Custom domain, isolated team compute</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>**$20.00**</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Production Database</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Neon Serverless Launch</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>10 GB Storage, automated daily backups</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>**$19.00**</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Encrypted Storage (R2)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Cloudflare R2 Standard</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>50 GB pooled storage baseline</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>**$0.75**</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Transactional Email</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Resend Pro</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>50,000 emails/mo, dedicated domain</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>**$20.00**</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Custom Domain &amp; DNS</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Cloudflare Registrar</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>`.com` / `.security` TLD</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>**$1.25**</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Payment Gateway</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Stripe Connect / Billing</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Automated subscription invoicing</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>**Variable**</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL FIXED INFRASTRUCTURE</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>**Baseline for ~10–25 Active Tenants**</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>**$61.00 / month**</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL DEMO INFRASTRUCTURE COST:</t>
+        </is>
+      </c>
+      <c r="E16" s="18">
+        <f>SUM(E2:E15)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Resources/WBS.xlsx
+++ b/Resources/WBS.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>352 Total Hours (264h Academic Baseline + 88h Commercial Extension)</t>
+          <t>424 Total Hours (264h Academic Baseline + 160h Commercial Launch across 18 Weeks)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Commercial Baseline &amp; Academic Evaluation Specification (Version 3.1.0)</t>
+          <t>Commercial Baseline &amp; Academic Evaluation Specification (Version 3.2.0)</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -856,12 +856,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>PostgreSQL Schema &amp; Row-Level Security</t>
+          <t>PostgreSQL Schema, Neon RLS &amp; Hash-Chained Audit</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Prisma relational schema, PostgreSQL RLS tenant context, and append-only audit grants</t>
+          <t>Prisma relational schema, PostgreSQL RLS tenant context, and append-only audit ledger with SHA-256 prev_hash</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Email / Password Auth &amp; JWT Sessions</t>
+          <t>Email / Password Auth &amp; Database-Backed Sessions</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Bcrypt password hashing (rounds = 12) and signed HTTP-only JWT cookies</t>
+          <t>Bcrypt/Argon2 password hashing, database-persisted session tokens, and secure HTTP-only cookies</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Token-Bucket Rate Limiter &amp; Pool RLS</t>
+          <t>Shared Store Rate Limiter &amp; Turnstile CAPTCHA</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Token-bucket rate limiting (5 req/hr/IP) on intake + dynamic tenant RLS</t>
+          <t>Shared store rate limiting (Postgres/Upstash) and Turnstile CAPTCHA (5 req/hr/IP)</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>WebCrypto Keypair Generator &amp; KeyStore</t>
+          <t>WebCrypto Keypair Generator &amp; Argon2 S2K KeyStore</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Ed25519 signing + X25519/RSA encryption subkeys in encrypted IndexedDB</t>
+          <t>Ed25519 signing + X25519 encryption keys stored in IndexedDB protected by OpenPGP Argon2 S2K</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Dual-Recipient OpenPGP Payload Encrypt</t>
+          <t>Multi-Recipient OpenPGP Payload Encrypt</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>In-browser payload encryption targeting Org encryption subkey + Hunter key with neutral operational labels</t>
+          <t>In-browser payload encryption targeting Org defenders + Hunter key with neutral operational labels</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>FR-3.4</t>
+          <t>FR-3.5</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Encrypted Attachment Upload (Cloudflare R2)</t>
+          <t>Direct-to-R2 Presigned Attachment Upload</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Client-side encrypted streaming binary uploads (≤ 25 MB) to R2</t>
+          <t>Client-side encrypted streaming binary uploads (≤ 25 MB) directly to Cloudflare R2 via presigned URLs</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Pure TypeScript CVSS 3.1 &amp; 52-Vector Test</t>
+          <t>Pure TypeScript CVSS 3.1 &amp; 45-Vector Test</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>GitHub REST API Commit SHA &amp; Author Check</t>
+          <t>GitHub REST API Commit SHA &amp; Branch Check</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>GitHub API v3 lookup validating commit existence, author, and branch for public and private repos</t>
+          <t>GitHub API v3 lookup validating commit existence and branch compare inclusion across public/private repos</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>WP-BUF</t>
+          <t>WP-BUF-1</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Auth Hardening &amp; Session Revocation</t>
+          <t>Auth Hardening, TOTP MFA &amp; Password Reset</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>TOTP MFA enrollment, password reset with immediate session revocation (JWT jti blacklisting), and MFA recovery codes</t>
+          <t>TOTP MFA enrollment, password reset with immediate session revocation, encrypted totp_secret at rest</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="G27" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Guided Onboarding &amp; Domain Verification</t>
+          <t>Guided Onboarding &amp; Offline Org Recovery Key</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Step-by-step wizard: DNS TXT verification, PGP key generation, RFC 9116 download, and public program activation</t>
+          <t>Step-by-step wizard: DNS verification, Offline Master Recovery Key generation, mandatory backup test challenge</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="G28" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>FR-1.5</t>
+          <t>FR-1.6</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Private Program Access &amp; Invite Lifecycle</t>
+          <t>Account-Less Guest Submission &amp; Tracking URLs</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Cryptographic invitation tokens (`token_hash` SHA-256 storage, 72h expiry, one-time redemption, uninvited email rejection)</t>
+          <t>Ephemeral Curve25519 key generation in browser, secret tracking URL issuance (`/report/track/BBT-RPT-XXXX`), anonymous retests</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="G29" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>WP-2.1</t>
+          <t>WP-4.1</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>FR-3.6</t>
+          <t>FR-8.4</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2206,17 +2206,17 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Multi-Defender Keying &amp; Session Re-Wrapping</t>
+          <t>Direct-to-R2 Presigned Upload &amp; Orphan Cleanup</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Local key export UI, program keyring versioning (`recipient_set_version`), and audited historical session-key re-wrapping</t>
+          <t>Presigned S3/R2 direct upload route (`/api/uploads/presign`), upload quota verification at issuance, and automated orphan cleanup</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>W15–W16</t>
+          <t>W13–W14</t>
         </is>
       </c>
       <c r="G30" s="9" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>WP-3.4</t>
+          <t>WP-4.2</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Notification Outbox Worker &amp; Deduplication</t>
+          <t>SLA Countdown Engine &amp; Slack Webhooks</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Outbox table pattern, exponential backoff retries, idempotency keys (no duplicate alerts), and minimal-metadata email templates</t>
+          <t>Hourly scheduled SLA cron check, notification outbox worker, visual countdown alerts, and Slack-compatible webhook payloads</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G31" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>FR-7.5</t>
+          <t>FR-7.7</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Redacted Evidence Export Engine</t>
+          <t>Redacted Evidence Export Engine (PDF &amp; JSON)</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Browser-side PDF/JSON export after local decryption. Excludes free-text exploit details by default; includes full preview before download</t>
+          <t>Sanitized PDF and JSON closure summary generation documenting timeline, commit SHA/branch, deployment env, and retest attestations</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>FR-8.4</t>
+          <t>FR-8.6</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Production Cloud &amp; Stripe Subscriptions</t>
+          <t>Merchant of Record (Lemon Squeezy) Billing</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Stripe Checkout, Customer Portal, webhook idempotency, failed payment grace periods, cancellation downgrade, and seat entitlement checks</t>
+          <t>Lemon Squeezy checkout integration (49/mo Team &amp; Free Tier), webhook handler, subscription downgrade, direct bank payouts to Pakistan</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>W17–W18</t>
+          <t>W15–W16</t>
         </is>
       </c>
       <c r="G33" s="11" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>WP-1.1</t>
+          <t>WP-2.1</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>FR-8.5</t>
+          <t>FR-2.1</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2406,21 +2406,21 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Disaster Recovery &amp; Incident Runbooks</t>
+          <t>Landing Page, Public Docs &amp; Legal Pack</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Automated daily PostgreSQL + R2 backup restore drill in sandbox, customer hard-deletion workflow, and incident response runbook</t>
+          <t>Marketing landing page, public documentation, free RFC 9116 generator tool, Terms of Service, Privacy Policy, DPA, and subprocessor list</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>W17–W18</t>
+          <t>W15–W16</t>
         </is>
       </c>
       <c r="G34" s="9" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>WP-1.2</t>
+          <t>WP-3.1</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
@@ -2446,57 +2446,257 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
+          <t>FR-8.1</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>MOD-7: Commercial Launch</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Application Security Hardening &amp; Pen-Test Pass</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Strict CSP, Subresource Integrity (SRI), CSRF protection on cookies, login/MFA lockout, SSRF checks on GitHub URLs, and self pen-test</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>W17–W18</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>WP-1.3</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>WP-7.10</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>NFR-01</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>MOD-7: Commercial Launch</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Observability (Sentry), Environments &amp; Uptime</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Sentry error tracking, staging and production database migrations in CI, and external uptime monitoring (BetterStack/UptimeRobot)</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>W17–W18</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>WP-1.1</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>WP-7.11</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>FR-1.2</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>MOD-7: Commercial Launch</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>SuperAdmin Abuse Management &amp; Console</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Administrative dashboard to inspect tenant counts, view platform error rates, handle abuse reports, and suspend abusive tenants</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>W13–W14</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>WP-2.3</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>WP-7.12</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>FR-8.7</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>MOD-7: Commercial Launch</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Disaster Recovery &amp; GDPR Hard Deletion</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Automated daily PostgreSQL + R2 backup restore drill in sandbox, customer hard-deletion workflow, and incident response runbook</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>W17–W18</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>WP-1.2</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>WP-BUF-2</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
           <t>GOV-02</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>GOV: Contingency &amp; Buffer</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>Commercial Launch Contingency Buffer</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Buffer for unexpected billing edge cases, webhook debugging, and production pilot support</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>W13–W18</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>Taha Asadullah</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>WP-7.1</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Commercial Pilot Support &amp; Launch Buffer</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Buffer for unexpected billing edge cases, webhook debugging, and production pilot customer support</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>W17–W18</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Taha Asadullah</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>WP-7.7</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
         <is>
           <t>[ROADMAP]</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="E36" s="13" t="inlineStr">
+    <row r="40">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED ENGINEERING HOURS:</t>
         </is>
       </c>
-      <c r="G36" s="14">
-        <f>SUM(G2:G35)</f>
-        <v>352</v>
+      <c r="G40" s="14">
+        <f>SUM(G2:G39)</f>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -2510,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2721,7 +2921,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Attested Retest, Peer Study &amp; Defense</t>
+          <t>Attested Retest &amp; Quota Management</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -2741,7 +2941,71 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Advised by Elena (QA) &amp; Alexander (PM)</t>
+          <t>Advised by Elena (QA) &amp; Garrison (SRE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>MOD-7</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Deployment, Billing &amp; Hardening</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>A / R</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Advised by Garrison (SRE) &amp; Nadia (Release)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>ACAD</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Usability Study &amp; FYP Defense</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>A / R</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Advised by Alexander (Steward) &amp; Victoria (Req)</t>
         </is>
       </c>
     </row>
@@ -2756,7 +3020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2818,21 +3082,21 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>WP-1.1, WP-1.2, WP-1.3, WP-1.4, Buffer (4h)</t>
+          <t>WP-1.1, WP-1.2, WP-1.3, WP-1.4</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Monorepo scaffolding, PostgreSQL RLS schema, AST Markdown sanitization, design tokens, BRD, SRS, WBS</t>
+          <t>Monorepo scaffolding, PostgreSQL RLS schema, AST sanitization, and UI tokens</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>Phase Gate 1 (DoR) Certified</t>
+          <t>Gate 0: Foundation Review</t>
         </is>
       </c>
       <c r="F2" s="9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
@@ -2853,21 +3117,21 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>WP-2.1, WP-2.2, WP-2.3, WP-2.4, Buffer (4h)</t>
+          <t>WP-2.1, WP-2.2, WP-2.3, WP-2.4</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Tenant registration wizard, bcrypt auth, JWT cookies, server RBAC, token-bucket rate limiter</t>
+          <t>Tenant registration, DB-backed sessions, server RBAC, and shared store rate limiter</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Phase Gate 2 (DoAC) Architecture</t>
+          <t>Gate 1: Identity &amp; Multi-Tenancy</t>
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -2888,21 +3152,21 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>WP-3.1, WP-3.2, WP-3.3, WP-3.4, Buffer (4h)</t>
+          <t>WP-3.1, WP-3.2, WP-3.3, WP-3.4</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Dynamic security.txt download API, browser cleartext PGP signing, DNS TXT check, WebCrypto keypairs</t>
+          <t>RFC 9116 download, in-browser PGP cleartext signing, DNS TXT verifier, Ed25519 keypair generator</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>Phase Gate 3 (DoCC) Core Crypto</t>
+          <t>Gate 2: Policy &amp; Keys</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -2923,21 +3187,21 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>WP-4.1, WP-4.2, WP-4.3, WP-4.4, Buffer (4h)</t>
+          <t>WP-4.1, WP-4.2, WP-4.3, WP-4.4</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Multi-recipient payload encryption, R2 attachment upload, CVSS 3.1 engine, in-browser decryption, basic triage</t>
+          <t>Dual-recipient encryption, direct R2 presigned upload, pure TS CVSS 3.1 engine, in-browser decryption</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Week 7 Live Working Prototype Milestone</t>
+          <t>Gate 3: Working Prototype Demonstration</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -2958,21 +3222,21 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>WP-5.1, WP-5.2, WP-5.3, WP-5.4, Buffer (6h)</t>
+          <t>WP-5.1, WP-5.2, WP-5.3, WP-5.4</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Dual-lane triage threads, Resend metadata alerts, duplicate linking, GitHub REST API commit validation</t>
+          <t>Dual-lane triage threads, metadata email alerts, GitHub commit &amp; branch compare validation, config SHA binder</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>Phase Gate 4 (DoQV) Triage &amp; VCS</t>
+          <t>Gate 4: Remediation Evidence</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -2993,21 +3257,21 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>WP-6.1, WP-6.2, ACAD-01, ACAD-02, Buffer (6h)</t>
+          <t>WP-6.1, WP-6.2, ACAD-01, ACAD-02, WP-BUF-1</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Attested retest engine, storage quotas, peer study (3–5 peers), Final FYP Report &amp; Defense</t>
+          <t>Attested retest state machine, storage quotas, Juice Shop usability study, final thesis &amp; demo defense</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Final FYP Defense &amp; Demonstration</t>
+          <t>Gate 5: Academic FYP Defense Certified</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -3023,26 +3287,26 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Weeks 13–15</t>
+          <t>Weeks 13–14</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>WP-7.1, WP-7.2, WP-7.3, WP-7.4, Buffer (4h)</t>
+          <t>WP-7.1, WP-7.2, WP-7.3, WP-7.4, WP-7.11</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>TOTP MFA, session revocation, guided onboarding wizard, tokenized private programs, multi-defender key management</t>
+          <t>TOTP MFA, offline recovery key onboarding, account-less guest intake, direct R2 upload hardening, SuperAdmin</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Milestone 3: Controlled Commercial Pilot</t>
+          <t>Gate 6: Commercial Core Intake</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -3058,26 +3322,26 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Weeks 16–18</t>
+          <t>Weeks 15–16</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>WP-7.5, WP-7.6, WP-7.7, WP-7.8, Buffer (6h)</t>
+          <t>WP-7.5, WP-7.6, WP-7.7, WP-7.8</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Notification outbox worker, redacted evidence export engine, Stripe subscription lifecycle, DR sandbox restore</t>
+          <t>SLA countdown engine &amp; Slack webhooks, redacted PDF export, Lemon Squeezy MoR billing, landing page &amp; legal</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Milestone 4: Commercial Launch Gate (DoRG)</t>
+          <t>Gate 7: Commercial Operations Ready</t>
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -3086,14 +3350,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="E10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Weeks 17–18</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>WP-7.9, WP-7.10, WP-7.12, WP-BUF-2</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Security hardening &amp; pen-test pass, Sentry observability, disaster recovery sandbox drill, launch buffer</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Gate 8: Commercial Production Release</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>[ROADMAP]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>TOTAL PLANNED SPRINT HOURS:</t>
         </is>
       </c>
-      <c r="F10" s="14">
-        <f>SUM(F2:F9)</f>
-        <v>352</v>
+      <c r="F11" s="14">
+        <f>SUM(F2:F10)</f>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -3107,7 +3406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3147,7 +3446,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Client Web &amp; API Gateway</t>
+          <t>Application &amp; API Gateway</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -3157,16 +3456,16 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Hobby / Free Tier</t>
+          <t>Hobby Developer Tier</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Serverless Functions, Edge CDN, Global SSL</t>
+          <t>Edge CDN, serverless functions, global SSL certificate</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -3177,27 +3476,27 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Neon Serverless Cloud</t>
+          <t>Neon Serverless</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Free Tier</t>
+          <t>PostgreSQL Free Tier</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>PostgreSQL 16 (512 MB Storage, Shared Compute, Dynamic RLS)</t>
+          <t>512 MB storage, connection pooling via PgBouncer (50 MB / tenant demo)</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Encrypted Object Storage</t>
+          <t>Encrypted File Storage</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -3207,16 +3506,16 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Free Tier</t>
+          <t>Free Tier Object Storage</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>10 GB Storage, Zero Egress Fees</t>
+          <t>10 GB storage allowance, zero egress bandwidth fees (2 GB / tenant demo)</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -3232,276 +3531,51 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Free Developer Tier</t>
+          <t>Developer Free Tier</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>100 Emails / Day, 3,000 Emails / Month</t>
+          <t>3,000 minimal-metadata triage notifications / month</t>
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Source Code &amp; CI/CD</t>
+          <t>CI/CD Build Automation</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>GitHub Free Tier</t>
+          <t>GitHub Actions</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Public Repository</t>
+          <t>Standard Runner Free Tier</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>2,000 Action Minutes / Month, REST API v3 Integration</t>
+          <t>2,000 automated build &amp; test minutes / month</t>
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>DNS Resolution</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>System DNS Resolver</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Free Native</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Node.js `dns.promises` Resolver for Domain Validation</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Domain &amp; SSL</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Local / Vercel Subdomain</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Free Tier</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>`.vercel.app` Free Subdomain with Automatic TLS Certificate</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Production Web Hosting</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Vercel Pro</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Custom domain, isolated team compute</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>**$20.00**</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Production Database</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Neon Serverless Launch</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>10 GB Storage, automated daily backups</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>**$19.00**</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Encrypted Storage (R2)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Cloudflare R2 Standard</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>50 GB pooled storage baseline</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>**$0.75**</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Transactional Email</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Resend Pro</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>50,000 emails/mo, dedicated domain</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>**$20.00**</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Custom Domain &amp; DNS</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Cloudflare Registrar</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>`.com` / `.security` TLD</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>**$1.25**</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Payment Gateway</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Stripe Connect / Billing</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Automated subscription invoicing</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>**Variable**</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL FIXED INFRASTRUCTURE</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>**Baseline for ~10–25 Active Tenants**</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>**$61.00 / month**</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>TOTAL DEMO INFRASTRUCTURE COST:</t>
         </is>
       </c>
-      <c r="E16" s="18">
-        <f>SUM(E2:E15)</f>
+      <c r="E7" s="18">
+        <f>SUM(E2:E6)</f>
         <v>0</v>
       </c>
     </row>

--- a/Resources/WBS.xlsx
+++ b/Resources/WBS.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>[DONE]</t>
+          <t>[READY]</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>[DONE]</t>
+          <t>[READY]</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>[DONE]</t>
+          <t>[READY]</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>[DONE]</t>
+          <t>[READY]</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>[READY]</t>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>[DONE]</t>
+          <t>[READY]</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>[READY]</t>
+          <t>[PLANNED]</t>
         </is>
       </c>
     </row>

--- a/Resources/WBS.xlsx
+++ b/Resources/WBS.xlsx
@@ -2156,12 +2156,12 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Account-Less Guest Submission &amp; Tracking URLs</t>
+          <t>Account-Less Guest Submission, Recovery &amp; Invitations</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Ephemeral Curve25519 key generation in browser, secret tracking URL issuance (`/report/track/BBT-RPT-XXXX`), anonymous retests</t>
+          <t>Ephemeral Curve25519 key generation in browser, secret tracking URL issuance with client URI fragment (#token=...&amp;key=...), exportable Guest Recovery Package, multi-device restoration UI (/report/restore), and tokenized private program access enforcement</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>WP-1.1, WP-1.2, WP-1.3, WP-1.4</t>
+          <t>WP-1.1 to WP-1.4 + Buffer (4h)</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="F2" s="9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>WP-2.1, WP-2.2, WP-2.3, WP-2.4</t>
+          <t>WP-2.1 to WP-2.4 + Buffer (4h)</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>WP-3.1, WP-3.2, WP-3.3, WP-3.4</t>
+          <t>WP-3.1 to WP-3.4 + Buffer (4h)</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>WP-4.1, WP-4.2, WP-4.3, WP-4.4</t>
+          <t>WP-4.1 to WP-4.4 + Buffer (4h)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>WP-5.1, WP-5.2, WP-5.3, WP-5.4</t>
+          <t>WP-5.1 to WP-5.4 + Buffer (6h)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>WP-6.1, WP-6.2, ACAD-01, ACAD-02, WP-BUF-1</t>
+          <t>WP-6.1, WP-6.2, ACAD-01, ACAD-02 + Defense Buffer (6h)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>TOTP MFA, offline recovery key onboarding, account-less guest intake, direct R2 upload hardening, SuperAdmin</t>
+          <t>TOTP MFA, offline recovery key onboarding, account-less guest intake &amp; recovery, direct R2 upload hardening, SuperAdmin</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">

--- a/Resources/WBS.xlsx
+++ b/Resources/WBS.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Session 2024–2028 / Batch 24-SET-Fall / Section SET-A</t>
+          <t>Session 2024–2028 / Batch 24-SET-Fall / Section SET-B</t>
         </is>
       </c>
     </row>

--- a/Resources/WBS.xlsx
+++ b/Resources/WBS.xlsx
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F1" s="15" t="inlineStr">
         <is>
-          <t>Internal AI Advisory Squad</t>
+          <t>Technical Standards &amp; Reference</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Advised by Arthur (Arch) &amp; Cyra (Sec)</t>
+          <t>PostgreSQL Row-Level Security &amp; OWASP ASVS v4.0</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Advised by Marcus (Forge) &amp; Cyra (Sec)</t>
+          <t>NIST SP 800-63B Authentication &amp; Multi-Tenant RBAC</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Advised by Victoria (Req) &amp; Cyra (Sec)</t>
+          <t>IETF RFC 9116 (security.txt) &amp; W3C WebCrypto API</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Advised by Cyra (Sec) &amp; Elena (QA)</t>
+          <t>IETF RFC 9580 (OpenPGP v6) &amp; FIRST CVSS 3.1 Standard</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Advised by Marcus (Forge) &amp; Julian (UX)</t>
+          <t>GitHub REST API v3 &amp; ISO/IEC 29147 Vulnerability Disclosure</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Advised by Elena (QA) &amp; Garrison (SRE)</t>
+          <t>ISO/IEC 30111 Vulnerability Handling Processes</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Advised by Garrison (SRE) &amp; Nadia (Release)</t>
+          <t>SaaS Merchant-of-Record &amp; Cloud Security Hardening</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Advised by Alexander (Steward) &amp; Victoria (Req)</t>
+          <t>IEEE 830-1998 Standards &amp; PTUT FYP Evaluation Criteria</t>
         </is>
       </c>
     </row>
